--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042735</v>
       </c>
       <c r="B2" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136348993</v>
       </c>
       <c r="B3" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136348995</v>
       </c>
       <c r="B4" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042735</v>
       </c>
       <c r="B2" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136348993</v>
       </c>
       <c r="B3" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136348995</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136348993</v>
       </c>
       <c r="B3" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136348995</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136347701</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136348994</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136348993</v>
       </c>
       <c r="B3" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136348995</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136348993</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136348995</v>
       </c>
       <c r="B4" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136347701</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136348994</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
         <v>136348993</v>
       </c>
       <c r="B3" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136348995</v>
       </c>
       <c r="B4" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136347701</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136348994</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,6 +1250,236 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136348994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137036318</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storbäckmyran, Arvidsträsk, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>771894</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7287375</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med gula apothecier</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137036318</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137036321</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storbäckmyran, Arvidsträsk, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>771719</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7287643</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med gula apotecier</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137036321</t>
         </is>
       </c>
     </row>
@@ -1260,6 +1490,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1285,11 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1400,11 +1396,7 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>137036318</v>
       </c>
       <c r="B7" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137036321</v>
       </c>
       <c r="B8" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136348993</v>
+        <v>137321234</v>
       </c>
       <c r="B3" t="n">
-        <v>93407</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,41 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Hötjärnbäcken, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771693</v>
+        <v>771963</v>
       </c>
       <c r="R3" t="n">
-        <v>7287616</v>
+        <v>7287352</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,17 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,69 +896,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136348993</t>
+          <t>https://artportalen.se/Sighting/137321234</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136348995</v>
+        <v>137321233</v>
       </c>
       <c r="B4" t="n">
-        <v>92138</v>
+        <v>97541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Hötjärnbäcken, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>771816</v>
+        <v>771980</v>
       </c>
       <c r="R4" t="n">
-        <v>7287534</v>
+        <v>7287335</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,17 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,66 +1008,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136348995</t>
+          <t>https://artportalen.se/Sighting/137321233</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136347701</v>
+        <v>137321235</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>97541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Hötjärnbäcken, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>771753</v>
+        <v>771885</v>
       </c>
       <c r="R5" t="n">
-        <v>7287396</v>
+        <v>7287397</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,27 +1090,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,49 +1120,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136347701</t>
+          <t>https://artportalen.se/Sighting/137321235</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136348994</v>
+        <v>136348993</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>93407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>771795</v>
+        <v>771693</v>
       </c>
       <c r="R6" t="n">
-        <v>7287606</v>
+        <v>7287616</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,16 +1242,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136348994</t>
+          <t>https://artportalen.se/Sighting/136348993</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137036318</v>
+        <v>136348995</v>
       </c>
       <c r="B7" t="n">
-        <v>79555</v>
+        <v>92138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,40 +1259,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>260591</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storbäckmyran, Arvidsträsk, Älvsbyn, Nb</t>
+          <t>Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>771894</v>
+        <v>771816</v>
       </c>
       <c r="R7" t="n">
-        <v>7287375</v>
+        <v>7287534</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,17 +1317,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Med gula apothecier</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,72 +1336,72 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137036318</t>
+          <t>https://artportalen.se/Sighting/136348995</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137036321</v>
+        <v>136347701</v>
       </c>
       <c r="B8" t="n">
-        <v>79555</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storbäckmyran, Arvidsträsk, Älvsbyn, Nb</t>
+          <t>Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>771719</v>
+        <v>771753</v>
       </c>
       <c r="R8" t="n">
-        <v>7287643</v>
+        <v>7287396</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,17 +1428,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Med gula apotecier</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,25 +1457,805 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136347701</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136348994</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>771795</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7287606</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136348994</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137321240</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79533</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hötjärnbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>771712</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7287641</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137321240</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137321241</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79533</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hötjärnbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>771691</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7287378</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137321241</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137321238</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79557</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hötjärnbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>771781</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7287634</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137321238</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137036318</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79556</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storbäckmyran, Arvidsträsk, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>771894</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7287375</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med gula apothecier</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137036318</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137036321</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79556</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storbäckmyran, Arvidsträsk, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>771719</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7287643</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med gula apotecier</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137036321</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137321237</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79556</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hötjärnbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>771781</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7287634</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137321237</t>
         </is>
       </c>
     </row>
@@ -1484,6 +2268,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137321234</v>
       </c>
       <c r="B3" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137321233</v>
       </c>
       <c r="B4" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137321235</v>
       </c>
       <c r="B5" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>137321240</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>137321241</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137321238</v>
       </c>
       <c r="B12" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137036318</v>
       </c>
       <c r="B13" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>137036321</v>
       </c>
       <c r="B14" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137321237</v>
       </c>
       <c r="B15" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 36806-2026 artfynd.xlsx
+++ b/artfynd/A 36806-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137321234</v>
       </c>
       <c r="B3" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137321233</v>
       </c>
       <c r="B4" t="n">
-        <v>97544</v>
+        <v>97548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137321235</v>
       </c>
       <c r="B5" t="n">
-        <v>97544</v>
+        <v>97548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>137321240</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>137321241</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137321238</v>
       </c>
       <c r="B12" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137036318</v>
       </c>
       <c r="B13" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>137036321</v>
       </c>
       <c r="B14" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137321237</v>
       </c>
       <c r="B15" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
